--- a/Datas/SleepSetDataList.xlsx
+++ b/Datas/SleepSetDataList.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>SleepSetData</t>
   </si>
@@ -68,16 +68,21 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>。。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>睡到早上7点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>睡到晚上7点</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SleepTime</t>
+  </si>
+  <si>
+    <t>SleepSun</t>
+  </si>
+  <si>
+    <t>SleepMoon</t>
   </si>
 </sst>
 </file>
@@ -478,7 +483,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -501,7 +506,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -512,7 +517,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" t="b">
         <v>1</v>
@@ -524,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F6">
         <v>19</v>
@@ -535,7 +540,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" t="b">
         <v>1</v>
@@ -547,7 +552,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F7">
         <v>7</v>

--- a/Datas/SleepSetDataList.xlsx
+++ b/Datas/SleepSetDataList.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>SleepSetData</t>
   </si>
@@ -47,9 +47,6 @@
     <t>text</t>
   </si>
   <si>
-    <t>icon</t>
-  </si>
-  <si>
     <t>startHour</t>
   </si>
   <si>
@@ -83,6 +80,18 @@
   </si>
   <si>
     <t>SleepMoon</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gameDay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iconName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -407,15 +416,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="14.875" customWidth="1"/>
-    <col min="4" max="4" width="27.125" customWidth="1"/>
+    <col min="2" max="3" width="14.875" customWidth="1"/>
+    <col min="5" max="5" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -423,30 +432,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -454,116 +466,131 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>6</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="b">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" t="b">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>14</v>
       </c>
       <c r="B6" t="b">
         <v>1</v>
       </c>
       <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
         <v>7</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6">
         <v>19</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" t="b">
         <v>1</v>
       </c>
       <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
         <v>19</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7">
         <v>7</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>19</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>